--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486719_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486719_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.361599999999999</v>
+        <v>9.3079</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9075</v>
+        <v>4.8041</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4541</v>
+        <v>4.5037</v>
       </c>
       <c r="G2" t="n">
         <v>3.6248</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>0.833</v>
+        <v>0.7792</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6891</v>
+        <v>0.5857</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1438</v>
+        <v>0.1935</v>
       </c>
       <c r="V2" t="n">
         <v>4.1315</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.791</v>
+        <v>6.1053</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2638</v>
+        <v>3.6775</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5272</v>
+        <v>2.4278</v>
       </c>
       <c r="G3" t="n">
         <v>3.4076</v>
@@ -688,13 +688,13 @@
         <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1546</v>
+        <v>0.469</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1652</v>
+        <v>0.5789</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0106</v>
+        <v>-0.1099</v>
       </c>
       <c r="V3" t="n">
         <v>0.4911</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4746</v>
+        <v>2.9491</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4043</v>
+        <v>-1.5077</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8789</v>
+        <v>4.4567</v>
       </c>
       <c r="G4" t="n">
         <v>4.0468</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.574</v>
+        <v>0.0484</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0546</v>
+        <v>-0.0488</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5194</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.2055</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9796</v>
+        <v>1.6208</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8763</v>
+        <v>-1.3592</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8559</v>
+        <v>2.98</v>
       </c>
       <c r="G5" t="n">
         <v>0.7161</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1584</v>
+        <v>-0.5171</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6622</v>
+        <v>-0.1451</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4962</v>
+        <v>-0.3721</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1228</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0074</v>
+        <v>0.4459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5393</v>
+        <v>0.953</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5319</v>
+        <v>-0.5071</v>
       </c>
       <c r="G6" t="n">
         <v>0.4144</v>
@@ -922,13 +922,13 @@
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3144</v>
+        <v>0.1241</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1932</v>
+        <v>0.2205</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1212</v>
+        <v>-0.0964</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3624</v>
+        <v>-0.5171</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8105</v>
+        <v>-0.9852</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4481</v>
+        <v>0.468</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3734</v>
+        <v>1.5034</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3499</v>
+        <v>0.2556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9765</v>
+        <v>1.2478</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8819</v>
+        <v>-0.0886</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3145</v>
+        <v>0.6009</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5674</v>
+        <v>-0.6895</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5085</v>
+        <v>1.592</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0354</v>
+        <v>-0.3453</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5439</v>
+        <v>1.9373</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3169</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4893</v>
+        <v>-0.0551</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5163</v>
+        <v>-0.1934</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0269</v>
+        <v>0.1383</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8645</v>
+        <v>-0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0.486</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3505</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5668</v>
+        <v>-0.7694</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9852</v>
+        <v>-1.1522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4184</v>
+        <v>0.3828</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5034</v>
+        <v>-2.1872</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2556</v>
+        <v>-1.1382</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2478</v>
+        <v>-1.0489</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0886</v>
+        <v>-1.2348</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6009</v>
+        <v>-0.586</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6895</v>
+        <v>-0.6488</v>
       </c>
       <c r="M8" t="n">
-        <v>1.592</v>
+        <v>-0.9524</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3453</v>
+        <v>-0.5522</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9373</v>
+        <v>-0.4002</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3515</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1048</v>
+        <v>-0.262</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1934</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0886</v>
+        <v>-0.3446</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6138</v>
+        <v>0.3282</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8415</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0589</v>
+        <v>-0.9449</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5659</v>
+        <v>-0.7034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.507</v>
+        <v>-0.2415</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1872</v>
+        <v>-0.9587</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1382</v>
+        <v>-0.8275</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0489</v>
+        <v>-0.1311</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2348</v>
+        <v>-0.6895</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.586</v>
+        <v>-0.6895</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9524</v>
+        <v>-0.2692</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5522</v>
+        <v>-0.1381</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4002</v>
+        <v>-0.1311</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5515</v>
+        <v>0.0138</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3311</v>
+        <v>-0.0139</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2204</v>
+        <v>0.0277</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2511</v>
+        <v>-1.2932</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9102</v>
+        <v>-2.7413</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3409</v>
+        <v>1.4481</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9587</v>
+        <v>-1.3734</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8275</v>
+        <v>-2.3499</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1311</v>
+        <v>0.9765</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6895</v>
+        <v>-1.8819</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6895</v>
+        <v>-1.3145</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.5674</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2692</v>
+        <v>0.5085</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1381</v>
+        <v>-1.0354</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1311</v>
+        <v>1.5439</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.3169</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2924</v>
+        <v>0.5585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2207</v>
+        <v>0.5855</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0717</v>
+        <v>-0.0269</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.8645</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9395</v>
+        <v>-2.9477</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5583</v>
+        <v>-1.7652</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3812</v>
+        <v>-1.1825</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4828</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5573</v>
+        <v>-0.5655</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6949</v>
+        <v>-0.4963</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8995</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1256</v>
+        <v>-3.6469</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8256</v>
+        <v>-3.4461</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3001</v>
+        <v>-0.2007</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5395</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4798</v>
+        <v>-0.0414</v>
       </c>
       <c r="T12" t="n">
-        <v>0.965</v>
+        <v>0.3445</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4852</v>
+        <v>-0.3859</v>
       </c>
       <c r="V12" t="n">
         <v>0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3099</v>
+        <v>10.3098</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.225700000000002</v>
+        <v>-4.2257</v>
       </c>
       <c r="F13" t="n">
-        <v>14.5355</v>
+        <v>14.5353</v>
       </c>
       <c r="G13" t="n">
         <v>5.171500000000002</v>
@@ -1459,7 +1459,7 @@
         <v>9.098500000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9309</v>
+        <v>1.930900000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.481</v>
@@ -1474,7 +1474,7 @@
         <v>1.9273</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3753</v>
+        <v>-1.3754</v>
       </c>
       <c r="V13" t="n">
         <v>2.6557</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7949</v>
+        <v>3.1562</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2863</v>
+        <v>2.4676</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.6886</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4176</v>
+        <v>2.8984</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6964</v>
+        <v>1.7794</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7211</v>
+        <v>1.119</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3229</v>
+        <v>2.9546</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6288</v>
+        <v>2.2629</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6918</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.0563</v>
       </c>
       <c r="N14" t="n">
-        <v>0.06759999999999999</v>
+        <v>-0.4835</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0271</v>
+        <v>0.4272</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7723</v>
+        <v>0.7723</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0892</v>
+        <v>-1.1585</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3169</v>
+        <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>3.663</v>
+        <v>0.4276</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8676</v>
+        <v>0.3858</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7954</v>
+        <v>0.0418</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5133</v>
+        <v>-0.9421</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1851</v>
+        <v>0.2856</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6984</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4144</v>
+        <v>2.4136</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6402</v>
+        <v>0.5384</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7742</v>
+        <v>1.8752</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8984</v>
+        <v>0.607</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7794</v>
+        <v>0.3176</v>
       </c>
       <c r="I15" t="n">
-        <v>1.119</v>
+        <v>0.2893</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9546</v>
+        <v>0.2491</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2629</v>
+        <v>0.2491</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6918</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0563</v>
+        <v>0.3579</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4835</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4272</v>
+        <v>0.2893</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3142</v>
+        <v>0.8413</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4416</v>
+        <v>0.4824</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1274</v>
+        <v>0.3589</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2675</v>
+        <v>1.4008</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3316</v>
+        <v>1.4247</v>
       </c>
       <c r="F16" t="n">
-        <v>1.936</v>
+        <v>-0.0239</v>
       </c>
       <c r="G16" t="n">
-        <v>0.607</v>
+        <v>2.4176</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3176</v>
+        <v>1.6964</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2893</v>
+        <v>0.7211</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2491</v>
+        <v>2.3229</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2491</v>
+        <v>1.6288</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3579</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2893</v>
+        <v>0.0271</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9654</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1931</v>
+        <v>-3.0892</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1585</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6952</v>
+        <v>1.2688</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2756</v>
+        <v>1.006</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4196</v>
+        <v>0.2628</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.6984</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7595</v>
+        <v>-2.3788</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4668</v>
+        <v>-2.2599</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2927</v>
+        <v>-0.1188</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7854</v>
@@ -1780,13 +1780,13 @@
         <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5187</v>
+        <v>-0.138</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0545</v>
+        <v>0.2613</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.3993</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8415</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8669</v>
+        <v>-2.7179</v>
       </c>
       <c r="E18" t="n">
         <v>-3.8354</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9685</v>
+        <v>1.1175</v>
       </c>
       <c r="G18" t="n">
         <v>-3.6225</v>
@@ -1858,13 +1858,13 @@
         <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0593</v>
+        <v>-0.9103</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3314</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7278</v>
+        <v>-0.5788</v>
       </c>
       <c r="V18" t="n">
         <v>0.6565</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.32</v>
+        <v>-3.6694</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2805</v>
+        <v>-5.6136</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0395</v>
+        <v>1.9442</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2978</v>
+        <v>-1.4765</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4683</v>
+        <v>-0.6898</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.7662</v>
+        <v>-0.7867</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.2419</v>
+        <v>-2.3034</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1242</v>
+        <v>-0.9651</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.366</v>
+        <v>-1.3383</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.056</v>
+        <v>0.8269</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3442</v>
+        <v>0.2753</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4002</v>
+        <v>0.5516</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9654</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3737</v>
+        <v>-0.6483</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9381</v>
+        <v>-0.414</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4356</v>
+        <v>-0.2342</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3463</v>
+        <v>-3.7324</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1835</v>
+        <v>-2.8668</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1629</v>
+        <v>-0.8656</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9121</v>
+        <v>-3.2978</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2685</v>
+        <v>0.4683</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1807</v>
+        <v>-3.7662</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0418</v>
+        <v>-3.2419</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7522</v>
+        <v>0.1242</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.794</v>
+        <v>-3.366</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8703</v>
+        <v>-0.056</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4837</v>
+        <v>0.3442</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3866</v>
+        <v>-0.4002</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.8616</v>
+        <v>0.9654</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.9854</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1712</v>
+        <v>-0.7862</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7167</v>
+        <v>-0.5244</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8878</v>
+        <v>-0.2618</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5985</v>
+        <v>-0.6138</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1271</v>
+        <v>0.8995</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5286</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4941</v>
+        <v>-4.0924</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0273</v>
+        <v>-4.3903</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5332</v>
+        <v>0.2979</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4765</v>
+        <v>-1.9121</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6898</v>
+        <v>1.2685</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7867</v>
+        <v>-3.1807</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3034</v>
+        <v>-1.0418</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9651</v>
+        <v>1.7522</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3383</v>
+        <v>-2.794</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8269</v>
+        <v>-0.8703</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2753</v>
+        <v>-0.4837</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5516</v>
+        <v>-0.3866</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5446</v>
+        <v>-3.8616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8962</v>
+        <v>-5.9854</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.473</v>
+        <v>0.0827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8277</v>
+        <v>0.5098</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6453</v>
+        <v>-0.4271</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5985</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5286</v>
       </c>
     </row>
     <row r="22">
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.31</v>
+        <v>-9.620299999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.5354</v>
+        <v>-14.5353</v>
       </c>
       <c r="F22" t="n">
-        <v>4.2254</v>
+        <v>4.9151</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.171299999999999</v>
+        <v>-5.171300000000001</v>
       </c>
       <c r="H22" t="n">
         <v>3.7916</v>
@@ -2152,13 +2152,13 @@
         <v>-9.0985</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5612</v>
+        <v>-0.5612000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>-0.6966000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1353</v>
+        <v>0.1353000000000001</v>
       </c>
       <c r="P22" t="n">
         <v>-1.9307</v>
@@ -2170,13 +2170,13 @@
         <v>14.4809</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5518999999999998</v>
+        <v>0.1375999999999995</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3756</v>
+        <v>1.3755</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.9272</v>
+        <v>-1.2377</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6557</v>
